--- a/data/trans_orig/P79A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>503141</t>
+          <t>547488</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498676</t>
+          <t>542207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505046</t>
+          <t>549886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>444609</t>
+          <t>484368</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437738</t>
+          <t>476807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>447142</t>
+          <t>487366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>947750</t>
+          <t>1031856</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940800</t>
+          <t>1024147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>950863</t>
+          <t>1035848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449766</t>
+          <t>480517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443071</t>
+          <t>475094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>378454</t>
+          <t>417742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373218</t>
+          <t>412616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380815</t>
+          <t>420620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>828221</t>
+          <t>898260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>822111</t>
+          <t>890771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831739</t>
+          <t>902656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,69 +1411,69 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>2,94%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1337</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4189</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1524,67 +1524,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>659337</t>
+          <t>459609</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648644</t>
+          <t>450032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666250</t>
+          <t>465242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>185408</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>181977</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>187497</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>97,06%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165574</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162722</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166748</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>824911</t>
+          <t>645017</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>636483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831761</t>
+          <t>651318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>60432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21533</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48880</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>71655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>998380</t>
+          <t>1093887</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>979205</t>
+          <t>1071411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1011282</t>
+          <t>1105922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>965653</t>
+          <t>847792</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>956561</t>
+          <t>839807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>853060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1964032</t>
+          <t>1941680</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939976</t>
+          <t>1921399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1981704</t>
+          <t>1956084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36801</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43412</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60752</t>
+          <t>75695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>455744</t>
+          <t>540934</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445137</t>
+          <t>524675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463802</t>
+          <t>550419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>817225</t>
+          <t>801732</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>804534</t>
+          <t>788856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>825567</t>
+          <t>810954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1272969</t>
+          <t>1342666</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255629</t>
+          <t>1323119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1285547</t>
+          <t>1356386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44835</t>
+          <t>40093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>736646</t>
+          <t>818686</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>719211</t>
+          <t>805108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>745555</t>
+          <t>828166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>977153</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>957043</t>
+          <t>1041416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>987710</t>
+          <t>1065187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>82813</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>63375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90840</t>
+          <t>110807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69596</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>63656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93040</t>
+          <t>100402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>138782</t>
+          <t>162477</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110708</t>
+          <t>133890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169428</t>
+          <t>192977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3306874</t>
+          <t>3359663</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3285220</t>
+          <t>3331669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3327150</t>
+          <t>3379101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3508162</t>
+          <t>3555729</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3484718</t>
+          <t>3534991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3525110</t>
+          <t>3571737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6815036</t>
+          <t>6915392</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6784390</t>
+          <t>6884892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6843110</t>
+          <t>6943979</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
